--- a/diem_thi.xlsx
+++ b/diem_thi.xlsx
@@ -1,17 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\web tra cuu\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C761A524-DC44-4035-9B5F-42C68757660A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Xử lý điểm thi bằng Excel và Py" sheetId="1" r:id="rId5"/>
+    <sheet name="Xử lý điểm thi bằng Excel và Py" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="20">
   <si>
     <t>SBD</t>
   </si>
@@ -31,9 +40,6 @@
     <t>9B01</t>
   </si>
   <si>
-    <t>Nguyễn Văn An</t>
-  </si>
-  <si>
     <t>9.0</t>
   </si>
   <si>
@@ -68,23 +74,30 @@
   </si>
   <si>
     <t>6.0</t>
+  </si>
+  <si>
+    <t>Lương Quốc Anh</t>
+  </si>
+  <si>
+    <t>0.5</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="d.m"/>
+    <numFmt numFmtId="164" formatCode="d\.m"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
@@ -95,35 +108,40 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
@@ -131,7 +149,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -321,17 +339,20 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -348,92 +369,92 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="1">
+        <v>1</v>
+      </c>
+      <c r="D2" s="1">
+        <v>1</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="2">
+        <v>46149</v>
+      </c>
+      <c r="D3" s="2">
+        <v>46150</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="1" t="s">
+    </row>
+    <row r="4" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="2">
+        <v>46150</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" s="2">
-        <v>46150.0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="2">
-        <v>46149.0</v>
-      </c>
-      <c r="D3" s="2">
-        <v>46150.0</v>
-      </c>
-      <c r="E3" s="1" t="s">
+    </row>
+    <row r="5" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" s="2">
+        <v>46150</v>
+      </c>
+      <c r="E5" s="2">
+        <v>46150</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" s="2">
+        <v>46149</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="2">
-        <v>46150.0</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5" s="2">
-        <v>46150.0</v>
-      </c>
-      <c r="E5" s="2">
-        <v>46150.0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" s="2">
-        <v>46149.0</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/diem_thi.xlsx
+++ b/diem_thi.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\web tra cuu\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C761A524-DC44-4035-9B5F-42C68757660A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64D03B14-89A3-478E-8BDF-5DE5F4A84563}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -351,6 +351,9 @@
   </sheetPr>
   <dimension ref="A1:E6"/>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="23.453125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">

--- a/diem_thi.xlsx
+++ b/diem_thi.xlsx
@@ -1,26 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\web tra cuu\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64D03B14-89A3-478E-8BDF-5DE5F4A84563}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6190"/>
   </bookViews>
   <sheets>
-    <sheet name="Xử lý điểm thi bằng Excel và Py" sheetId="1" r:id="rId1"/>
+    <sheet name="Hướng dẫn nhập điểm và xếp hạng" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
   <si>
     <t>SBD</t>
   </si>
@@ -37,59 +36,155 @@
     <t>Anh</t>
   </si>
   <si>
-    <t>9B01</t>
-  </si>
-  <si>
-    <t>9.0</t>
-  </si>
-  <si>
-    <t>8.0</t>
-  </si>
-  <si>
-    <t>9B02</t>
-  </si>
-  <si>
-    <t>Trần Thị Bình</t>
-  </si>
-  <si>
-    <t>9B03</t>
-  </si>
-  <si>
-    <t>Lê Hoàng Cường</t>
-  </si>
-  <si>
-    <t>7.0</t>
-  </si>
-  <si>
-    <t>9B04</t>
-  </si>
-  <si>
-    <t>Phạm Khoa</t>
-  </si>
-  <si>
-    <t>9B05</t>
-  </si>
-  <si>
-    <t>Vũ Thị Ngọc</t>
-  </si>
-  <si>
-    <t>6.0</t>
-  </si>
-  <si>
     <t>Lương Quốc Anh</t>
   </si>
   <si>
-    <t>0.5</t>
+    <t>Nguyễn Thị Lan Anh</t>
+  </si>
+  <si>
+    <t>Phạm Hà Anh</t>
+  </si>
+  <si>
+    <t>Nguyễn Như Bách</t>
+  </si>
+  <si>
+    <t>Lê Phương Bắc</t>
+  </si>
+  <si>
+    <t>Nguyễn Gia Bảo</t>
+  </si>
+  <si>
+    <t>Nguyễn Trọng Đức</t>
+  </si>
+  <si>
+    <t>Hàn Thu Hà</t>
+  </si>
+  <si>
+    <t>Nguyễn Thu Hà</t>
+  </si>
+  <si>
+    <t>Nguyễn Thị Diễm Hằng</t>
+  </si>
+  <si>
+    <t>Lê Quang Hoàng</t>
+  </si>
+  <si>
+    <t>Nguyễn Thị Huệ</t>
+  </si>
+  <si>
+    <t>Nguyễn Ngọc Quang Huy</t>
+  </si>
+  <si>
+    <t>Nguyễn Nhật Huy</t>
+  </si>
+  <si>
+    <t>Nguyễn Tuấn Khanh</t>
+  </si>
+  <si>
+    <t>Lê Anh Khoa</t>
+  </si>
+  <si>
+    <t>Nguyễn Thị Chúc Linh</t>
+  </si>
+  <si>
+    <t>Nguyễn Thị Phương Linh</t>
+  </si>
+  <si>
+    <t>Nguyễn Trần Tuấn Linh</t>
+  </si>
+  <si>
+    <t>Tô Thị Hà Linh</t>
+  </si>
+  <si>
+    <t>Lê Ngọc Hoàng Long</t>
+  </si>
+  <si>
+    <t>Nguyễn Văn Long</t>
+  </si>
+  <si>
+    <t>Đặng Hương Ly</t>
+  </si>
+  <si>
+    <t>Nguyễn Thị Ly</t>
+  </si>
+  <si>
+    <t>Lê Ngọc Tùng Minh</t>
+  </si>
+  <si>
+    <t>Nguyễn Tiến Minh</t>
+  </si>
+  <si>
+    <t>Lê Minh Nam</t>
+  </si>
+  <si>
+    <t>Nguyễn Thị Nga</t>
+  </si>
+  <si>
+    <t>Đỗ Cao Ngọc</t>
+  </si>
+  <si>
+    <t>Nguyễn Hồng Nguyên</t>
+  </si>
+  <si>
+    <t>Nguyễn Ánh Nhi</t>
+  </si>
+  <si>
+    <t>Nguyễn Phương Nhi</t>
+  </si>
+  <si>
+    <t>Nguyễn Thị Yến Nhi</t>
+  </si>
+  <si>
+    <t>Nguyễn Bảo Như</t>
+  </si>
+  <si>
+    <t>Nguyễn Khắc Phong</t>
+  </si>
+  <si>
+    <t>Nguyễn Hà Phương</t>
+  </si>
+  <si>
+    <t>Lê Thị Phương Thơm</t>
+  </si>
+  <si>
+    <t>Nguyễn Thị Phương Trà</t>
+  </si>
+  <si>
+    <t>Nguyễn Thị Huyền Trang</t>
+  </si>
+  <si>
+    <t>Nguyễn Thị Thu Trang</t>
+  </si>
+  <si>
+    <t>Nguyễn Văn Trọng</t>
+  </si>
+  <si>
+    <t>Nguyễn Thanh Trúc</t>
+  </si>
+  <si>
+    <t>Nguyễn Phi Tùng</t>
+  </si>
+  <si>
+    <t>Nguyễn Bảo Uyên</t>
+  </si>
+  <si>
+    <t>Nguyễn Thị Phương Uyên</t>
+  </si>
+  <si>
+    <t>Lê Phương Vi</t>
+  </si>
+  <si>
+    <t>Nguyễn Tường Vy</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="d\.m"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -102,6 +197,12 @@
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -111,7 +212,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -119,14 +220,33 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+  <cellXfs count="5">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -345,14 +465,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E48"/>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="23.453125" customWidth="1"/>
+    <col min="2" max="2" width="24.90625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -373,91 +493,524 @@
       </c>
     </row>
     <row r="2" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2">
+        <v>262101</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="3"/>
+    </row>
+    <row r="3" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2">
+        <v>261102</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="1"/>
+    </row>
+    <row r="4" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
+        <v>262103</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="3"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+    </row>
+    <row r="5" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
+        <v>261104</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="1"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+    </row>
+    <row r="6" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
+        <v>261105</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="1"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="1"/>
+    </row>
+    <row r="7" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="2">
+        <v>261106</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+    </row>
+    <row r="8" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
+        <v>262107</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+    </row>
+    <row r="9" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2">
+        <v>261108</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+    </row>
+    <row r="10" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2">
+        <v>262109</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+    </row>
+    <row r="11" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2">
+        <v>262110</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+    </row>
+    <row r="12" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2">
+        <v>262111</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+    </row>
+    <row r="13" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="2">
+        <v>261112</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+    </row>
+    <row r="14" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="2">
+        <v>262113</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+    </row>
+    <row r="15" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="2">
+        <v>261114</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="1">
-        <v>1</v>
-      </c>
-      <c r="D2" s="1">
-        <v>1</v>
-      </c>
-      <c r="E2" s="2" t="s">
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+    </row>
+    <row r="16" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="2">
+        <v>262115</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="2">
-        <v>46149</v>
-      </c>
-      <c r="D3" s="2">
-        <v>46150</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="2">
-        <v>46150</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D5" s="2">
-        <v>46150</v>
-      </c>
-      <c r="E5" s="2">
-        <v>46150</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D6" s="2">
-        <v>46149</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>7</v>
-      </c>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+    </row>
+    <row r="17" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="2">
+        <v>262116</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+    </row>
+    <row r="18" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="2">
+        <v>262117</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+    </row>
+    <row r="19" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="2">
+        <v>261118</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C19" s="4"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+    </row>
+    <row r="20" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="2">
+        <v>261119</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C20" s="4"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+    </row>
+    <row r="21" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="2">
+        <v>262120</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C21" s="4"/>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4"/>
+    </row>
+    <row r="22" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="2">
+        <v>262121</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C22" s="4"/>
+      <c r="D22" s="4"/>
+      <c r="E22" s="4"/>
+    </row>
+    <row r="23" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="2">
+        <v>261122</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C23" s="4"/>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
+    </row>
+    <row r="24" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="2">
+        <v>262123</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C24" s="4"/>
+      <c r="D24" s="4"/>
+      <c r="E24" s="4"/>
+    </row>
+    <row r="25" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="2">
+        <v>261124</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C25" s="4"/>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4"/>
+    </row>
+    <row r="26" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="2">
+        <v>262201</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C26" s="4"/>
+      <c r="D26" s="4"/>
+      <c r="E26" s="4"/>
+    </row>
+    <row r="27" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="2">
+        <v>261202</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C27" s="4"/>
+      <c r="D27" s="4"/>
+      <c r="E27" s="4"/>
+    </row>
+    <row r="28" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="2">
+        <v>261203</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C28" s="4"/>
+      <c r="D28" s="4"/>
+      <c r="E28" s="4"/>
+    </row>
+    <row r="29" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="2">
+        <v>262204</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C29" s="4"/>
+      <c r="D29" s="4"/>
+      <c r="E29" s="4"/>
+    </row>
+    <row r="30" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="2">
+        <v>262205</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C30" s="4"/>
+      <c r="D30" s="4"/>
+      <c r="E30" s="4"/>
+    </row>
+    <row r="31" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="2">
+        <v>262206</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C31" s="4"/>
+      <c r="D31" s="4"/>
+      <c r="E31" s="4"/>
+    </row>
+    <row r="32" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="2">
+        <v>261207</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C32" s="4"/>
+      <c r="D32" s="4"/>
+      <c r="E32" s="4"/>
+    </row>
+    <row r="33" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="2">
+        <v>262208</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C33" s="4"/>
+      <c r="D33" s="4"/>
+      <c r="E33" s="4"/>
+    </row>
+    <row r="34" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="2">
+        <v>262209</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C34" s="4"/>
+      <c r="D34" s="4"/>
+      <c r="E34" s="4"/>
+    </row>
+    <row r="35" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="2">
+        <v>261210</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C35" s="4"/>
+      <c r="D35" s="4"/>
+      <c r="E35" s="4"/>
+    </row>
+    <row r="36" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="2">
+        <v>261211</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C36" s="4"/>
+      <c r="D36" s="4"/>
+      <c r="E36" s="4"/>
+    </row>
+    <row r="37" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="2">
+        <v>261212</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C37" s="4"/>
+      <c r="D37" s="4"/>
+      <c r="E37" s="4"/>
+    </row>
+    <row r="38" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="2">
+        <v>261213</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C38" s="4"/>
+      <c r="D38" s="4"/>
+      <c r="E38" s="4"/>
+    </row>
+    <row r="39" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="2">
+        <v>262214</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C39" s="4"/>
+      <c r="D39" s="4"/>
+      <c r="E39" s="4"/>
+    </row>
+    <row r="40" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="2">
+        <v>261215</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C40" s="4"/>
+      <c r="D40" s="4"/>
+      <c r="E40" s="4"/>
+    </row>
+    <row r="41" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="2">
+        <v>262216</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C41" s="4"/>
+      <c r="D41" s="4"/>
+      <c r="E41" s="4"/>
+    </row>
+    <row r="42" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="2">
+        <v>262217</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C42" s="4"/>
+      <c r="D42" s="4"/>
+      <c r="E42" s="4"/>
+    </row>
+    <row r="43" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="2">
+        <v>261218</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C43" s="4"/>
+      <c r="D43" s="4"/>
+      <c r="E43" s="4"/>
+    </row>
+    <row r="44" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="2">
+        <v>262219</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C44" s="4"/>
+      <c r="D44" s="4"/>
+      <c r="E44" s="4"/>
+    </row>
+    <row r="45" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="2">
+        <v>262220</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C45" s="4"/>
+      <c r="D45" s="4"/>
+      <c r="E45" s="4"/>
+    </row>
+    <row r="46" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="2">
+        <v>261221</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C46" s="4"/>
+      <c r="D46" s="4"/>
+      <c r="E46" s="4"/>
+    </row>
+    <row r="47" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="2">
+        <v>262222</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C47" s="4"/>
+      <c r="D47" s="4"/>
+      <c r="E47" s="4"/>
+    </row>
+    <row r="48" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="2">
+        <v>261223</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C48" s="4"/>
+      <c r="D48" s="4"/>
+      <c r="E48" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/diem_thi.xlsx
+++ b/diem_thi.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="73">
   <si>
     <t>SBD</t>
   </si>
@@ -175,6 +175,69 @@
   </si>
   <si>
     <t>Nguyễn Tường Vy</t>
+  </si>
+  <si>
+    <t>4,25</t>
+  </si>
+  <si>
+    <t>4,75</t>
+  </si>
+  <si>
+    <t>7,5</t>
+  </si>
+  <si>
+    <t>6,5</t>
+  </si>
+  <si>
+    <t>0,75</t>
+  </si>
+  <si>
+    <t>6,25</t>
+  </si>
+  <si>
+    <t>7,0</t>
+  </si>
+  <si>
+    <t>4,5</t>
+  </si>
+  <si>
+    <t>6,0</t>
+  </si>
+  <si>
+    <t>1,5</t>
+  </si>
+  <si>
+    <t>6,75</t>
+  </si>
+  <si>
+    <t>1,75</t>
+  </si>
+  <si>
+    <t>5,75</t>
+  </si>
+  <si>
+    <t>8,0</t>
+  </si>
+  <si>
+    <t>7,25</t>
+  </si>
+  <si>
+    <t>5,25</t>
+  </si>
+  <si>
+    <t>5,0</t>
+  </si>
+  <si>
+    <t>2,75</t>
+  </si>
+  <si>
+    <t>5,5</t>
+  </si>
+  <si>
+    <t>4,0</t>
+  </si>
+  <si>
+    <t>3,75</t>
   </si>
 </sst>
 </file>
@@ -239,7 +302,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -247,6 +310,10 @@
     </xf>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -473,6 +540,7 @@
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="24.90625" customWidth="1"/>
+    <col min="4" max="4" width="12.6328125" style="8"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -485,7 +553,7 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
@@ -500,7 +568,9 @@
         <v>5</v>
       </c>
       <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
+      <c r="D2" s="5" t="s">
+        <v>52</v>
+      </c>
       <c r="E2" s="3"/>
     </row>
     <row r="3" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -511,7 +581,9 @@
         <v>6</v>
       </c>
       <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
+      <c r="D3" s="6" t="s">
+        <v>53</v>
+      </c>
       <c r="E3" s="1"/>
     </row>
     <row r="4" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -522,7 +594,9 @@
         <v>7</v>
       </c>
       <c r="C4" s="3"/>
-      <c r="D4" s="1"/>
+      <c r="D4" s="5" t="s">
+        <v>54</v>
+      </c>
       <c r="E4" s="1"/>
     </row>
     <row r="5" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -533,7 +607,9 @@
         <v>8</v>
       </c>
       <c r="C5" s="1"/>
-      <c r="D5" s="3"/>
+      <c r="D5" s="6" t="s">
+        <v>54</v>
+      </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -544,7 +620,9 @@
         <v>9</v>
       </c>
       <c r="C6" s="1"/>
-      <c r="D6" s="3"/>
+      <c r="D6" s="6" t="s">
+        <v>55</v>
+      </c>
       <c r="E6" s="1"/>
     </row>
     <row r="7" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -555,7 +633,7 @@
         <v>10</v>
       </c>
       <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
+      <c r="D7" s="7"/>
       <c r="E7" s="4"/>
     </row>
     <row r="8" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -566,7 +644,9 @@
         <v>11</v>
       </c>
       <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
+      <c r="D8" s="7" t="s">
+        <v>56</v>
+      </c>
       <c r="E8" s="4"/>
     </row>
     <row r="9" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -577,7 +657,9 @@
         <v>12</v>
       </c>
       <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
+      <c r="D9" s="7" t="s">
+        <v>57</v>
+      </c>
       <c r="E9" s="4"/>
     </row>
     <row r="10" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -588,7 +670,9 @@
         <v>13</v>
       </c>
       <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
+      <c r="D10" s="7" t="s">
+        <v>58</v>
+      </c>
       <c r="E10" s="4"/>
     </row>
     <row r="11" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -599,7 +683,9 @@
         <v>14</v>
       </c>
       <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
+      <c r="D11" s="7" t="s">
+        <v>55</v>
+      </c>
       <c r="E11" s="4"/>
     </row>
     <row r="12" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -610,7 +696,9 @@
         <v>15</v>
       </c>
       <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
+      <c r="D12" s="7" t="s">
+        <v>59</v>
+      </c>
       <c r="E12" s="4"/>
     </row>
     <row r="13" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -621,7 +709,9 @@
         <v>16</v>
       </c>
       <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
+      <c r="D13" s="7" t="s">
+        <v>60</v>
+      </c>
       <c r="E13" s="4"/>
     </row>
     <row r="14" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -632,7 +722,9 @@
         <v>17</v>
       </c>
       <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
+      <c r="D14" s="7" t="s">
+        <v>61</v>
+      </c>
       <c r="E14" s="4"/>
     </row>
     <row r="15" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -643,7 +735,9 @@
         <v>18</v>
       </c>
       <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
+      <c r="D15" s="7" t="s">
+        <v>62</v>
+      </c>
       <c r="E15" s="4"/>
     </row>
     <row r="16" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -654,7 +748,9 @@
         <v>19</v>
       </c>
       <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
+      <c r="D16" s="7" t="s">
+        <v>63</v>
+      </c>
       <c r="E16" s="4"/>
     </row>
     <row r="17" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -665,7 +761,9 @@
         <v>20</v>
       </c>
       <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
+      <c r="D17" s="7" t="s">
+        <v>53</v>
+      </c>
       <c r="E17" s="4"/>
     </row>
     <row r="18" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -676,7 +774,9 @@
         <v>21</v>
       </c>
       <c r="C18" s="4"/>
-      <c r="D18" s="4"/>
+      <c r="D18" s="7" t="s">
+        <v>64</v>
+      </c>
       <c r="E18" s="4"/>
     </row>
     <row r="19" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -687,7 +787,9 @@
         <v>22</v>
       </c>
       <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
+      <c r="D19" s="7" t="s">
+        <v>60</v>
+      </c>
       <c r="E19" s="4"/>
     </row>
     <row r="20" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -698,7 +800,9 @@
         <v>23</v>
       </c>
       <c r="C20" s="4"/>
-      <c r="D20" s="4"/>
+      <c r="D20" s="7" t="s">
+        <v>62</v>
+      </c>
       <c r="E20" s="4"/>
     </row>
     <row r="21" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -709,7 +813,9 @@
         <v>24</v>
       </c>
       <c r="C21" s="4"/>
-      <c r="D21" s="4"/>
+      <c r="D21" s="7" t="s">
+        <v>60</v>
+      </c>
       <c r="E21" s="4"/>
     </row>
     <row r="22" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -720,7 +826,9 @@
         <v>25</v>
       </c>
       <c r="C22" s="4"/>
-      <c r="D22" s="4"/>
+      <c r="D22" s="7" t="s">
+        <v>65</v>
+      </c>
       <c r="E22" s="4"/>
     </row>
     <row r="23" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -731,7 +839,9 @@
         <v>26</v>
       </c>
       <c r="C23" s="4"/>
-      <c r="D23" s="4"/>
+      <c r="D23" s="7" t="s">
+        <v>59</v>
+      </c>
       <c r="E23" s="4"/>
     </row>
     <row r="24" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -742,7 +852,9 @@
         <v>27</v>
       </c>
       <c r="C24" s="4"/>
-      <c r="D24" s="4"/>
+      <c r="D24" s="7" t="s">
+        <v>66</v>
+      </c>
       <c r="E24" s="4"/>
     </row>
     <row r="25" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -753,7 +865,9 @@
         <v>28</v>
       </c>
       <c r="C25" s="4"/>
-      <c r="D25" s="4"/>
+      <c r="D25" s="7" t="s">
+        <v>64</v>
+      </c>
       <c r="E25" s="4"/>
     </row>
     <row r="26" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -764,7 +878,9 @@
         <v>29</v>
       </c>
       <c r="C26" s="4"/>
-      <c r="D26" s="4"/>
+      <c r="D26" s="7" t="s">
+        <v>67</v>
+      </c>
       <c r="E26" s="4"/>
     </row>
     <row r="27" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -775,7 +891,9 @@
         <v>30</v>
       </c>
       <c r="C27" s="4"/>
-      <c r="D27" s="4"/>
+      <c r="D27" s="7" t="s">
+        <v>68</v>
+      </c>
       <c r="E27" s="4"/>
     </row>
     <row r="28" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -786,7 +904,9 @@
         <v>31</v>
       </c>
       <c r="C28" s="4"/>
-      <c r="D28" s="4"/>
+      <c r="D28" s="7" t="s">
+        <v>60</v>
+      </c>
       <c r="E28" s="4"/>
     </row>
     <row r="29" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -797,7 +917,9 @@
         <v>32</v>
       </c>
       <c r="C29" s="4"/>
-      <c r="D29" s="4"/>
+      <c r="D29" s="7" t="s">
+        <v>65</v>
+      </c>
       <c r="E29" s="4"/>
     </row>
     <row r="30" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -808,7 +930,9 @@
         <v>33</v>
       </c>
       <c r="C30" s="4"/>
-      <c r="D30" s="4"/>
+      <c r="D30" s="7" t="s">
+        <v>68</v>
+      </c>
       <c r="E30" s="4"/>
     </row>
     <row r="31" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -819,7 +943,9 @@
         <v>34</v>
       </c>
       <c r="C31" s="4"/>
-      <c r="D31" s="4"/>
+      <c r="D31" s="7" t="s">
+        <v>69</v>
+      </c>
       <c r="E31" s="4"/>
     </row>
     <row r="32" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -830,7 +956,9 @@
         <v>35</v>
       </c>
       <c r="C32" s="4"/>
-      <c r="D32" s="4"/>
+      <c r="D32" s="7" t="s">
+        <v>57</v>
+      </c>
       <c r="E32" s="4"/>
     </row>
     <row r="33" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -841,7 +969,9 @@
         <v>36</v>
       </c>
       <c r="C33" s="4"/>
-      <c r="D33" s="4"/>
+      <c r="D33" s="7" t="s">
+        <v>60</v>
+      </c>
       <c r="E33" s="4"/>
     </row>
     <row r="34" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -852,7 +982,9 @@
         <v>37</v>
       </c>
       <c r="C34" s="4"/>
-      <c r="D34" s="4"/>
+      <c r="D34" s="7" t="s">
+        <v>64</v>
+      </c>
       <c r="E34" s="4"/>
     </row>
     <row r="35" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -863,7 +995,9 @@
         <v>38</v>
       </c>
       <c r="C35" s="4"/>
-      <c r="D35" s="4"/>
+      <c r="D35" s="7" t="s">
+        <v>64</v>
+      </c>
       <c r="E35" s="4"/>
     </row>
     <row r="36" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -874,7 +1008,9 @@
         <v>39</v>
       </c>
       <c r="C36" s="4"/>
-      <c r="D36" s="4"/>
+      <c r="D36" s="7" t="s">
+        <v>57</v>
+      </c>
       <c r="E36" s="4"/>
     </row>
     <row r="37" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -885,7 +1021,9 @@
         <v>40</v>
       </c>
       <c r="C37" s="4"/>
-      <c r="D37" s="4"/>
+      <c r="D37" s="7" t="s">
+        <v>58</v>
+      </c>
       <c r="E37" s="4"/>
     </row>
     <row r="38" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -896,7 +1034,9 @@
         <v>41</v>
       </c>
       <c r="C38" s="4"/>
-      <c r="D38" s="4"/>
+      <c r="D38" s="7" t="s">
+        <v>67</v>
+      </c>
       <c r="E38" s="4"/>
     </row>
     <row r="39" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -907,7 +1047,9 @@
         <v>42</v>
       </c>
       <c r="C39" s="4"/>
-      <c r="D39" s="4"/>
+      <c r="D39" s="7" t="s">
+        <v>54</v>
+      </c>
       <c r="E39" s="4"/>
     </row>
     <row r="40" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -918,7 +1060,9 @@
         <v>43</v>
       </c>
       <c r="C40" s="4"/>
-      <c r="D40" s="4"/>
+      <c r="D40" s="7" t="s">
+        <v>59</v>
+      </c>
       <c r="E40" s="4"/>
     </row>
     <row r="41" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -929,7 +1073,9 @@
         <v>44</v>
       </c>
       <c r="C41" s="4"/>
-      <c r="D41" s="4"/>
+      <c r="D41" s="7" t="s">
+        <v>70</v>
+      </c>
       <c r="E41" s="4"/>
     </row>
     <row r="42" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -940,7 +1086,9 @@
         <v>45</v>
       </c>
       <c r="C42" s="4"/>
-      <c r="D42" s="4"/>
+      <c r="D42" s="7" t="s">
+        <v>71</v>
+      </c>
       <c r="E42" s="4"/>
     </row>
     <row r="43" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -951,7 +1099,9 @@
         <v>46</v>
       </c>
       <c r="C43" s="4"/>
-      <c r="D43" s="4"/>
+      <c r="D43" s="7" t="s">
+        <v>54</v>
+      </c>
       <c r="E43" s="4"/>
     </row>
     <row r="44" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -962,7 +1112,9 @@
         <v>47</v>
       </c>
       <c r="C44" s="4"/>
-      <c r="D44" s="4"/>
+      <c r="D44" s="7" t="s">
+        <v>72</v>
+      </c>
       <c r="E44" s="4"/>
     </row>
     <row r="45" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -973,7 +1125,9 @@
         <v>48</v>
       </c>
       <c r="C45" s="4"/>
-      <c r="D45" s="4"/>
+      <c r="D45" s="7" t="s">
+        <v>68</v>
+      </c>
       <c r="E45" s="4"/>
     </row>
     <row r="46" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -984,7 +1138,9 @@
         <v>49</v>
       </c>
       <c r="C46" s="4"/>
-      <c r="D46" s="4"/>
+      <c r="D46" s="7" t="s">
+        <v>60</v>
+      </c>
       <c r="E46" s="4"/>
     </row>
     <row r="47" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -995,7 +1151,9 @@
         <v>50</v>
       </c>
       <c r="C47" s="4"/>
-      <c r="D47" s="4"/>
+      <c r="D47" s="7" t="s">
+        <v>60</v>
+      </c>
       <c r="E47" s="4"/>
     </row>
     <row r="48" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1006,7 +1164,9 @@
         <v>51</v>
       </c>
       <c r="C48" s="4"/>
-      <c r="D48" s="4"/>
+      <c r="D48" s="7" t="s">
+        <v>65</v>
+      </c>
       <c r="E48" s="4"/>
     </row>
   </sheetData>

--- a/diem_thi.xlsx
+++ b/diem_thi.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
   <si>
     <t>SBD</t>
   </si>
@@ -175,69 +175,6 @@
   </si>
   <si>
     <t>Nguyễn Tường Vy</t>
-  </si>
-  <si>
-    <t>4,25</t>
-  </si>
-  <si>
-    <t>4,75</t>
-  </si>
-  <si>
-    <t>7,5</t>
-  </si>
-  <si>
-    <t>6,5</t>
-  </si>
-  <si>
-    <t>0,75</t>
-  </si>
-  <si>
-    <t>6,25</t>
-  </si>
-  <si>
-    <t>7,0</t>
-  </si>
-  <si>
-    <t>4,5</t>
-  </si>
-  <si>
-    <t>6,0</t>
-  </si>
-  <si>
-    <t>1,5</t>
-  </si>
-  <si>
-    <t>6,75</t>
-  </si>
-  <si>
-    <t>1,75</t>
-  </si>
-  <si>
-    <t>5,75</t>
-  </si>
-  <si>
-    <t>8,0</t>
-  </si>
-  <si>
-    <t>7,25</t>
-  </si>
-  <si>
-    <t>5,25</t>
-  </si>
-  <si>
-    <t>5,0</t>
-  </si>
-  <si>
-    <t>2,75</t>
-  </si>
-  <si>
-    <t>5,5</t>
-  </si>
-  <si>
-    <t>4,0</t>
-  </si>
-  <si>
-    <t>3,75</t>
   </si>
 </sst>
 </file>
@@ -302,7 +239,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -310,10 +247,9 @@
     </xf>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -540,7 +476,7 @@
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="24.90625" customWidth="1"/>
-    <col min="4" max="4" width="12.6328125" style="8"/>
+    <col min="4" max="4" width="12.6328125" style="7"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -568,8 +504,8 @@
         <v>5</v>
       </c>
       <c r="C2" s="1"/>
-      <c r="D2" s="5" t="s">
-        <v>52</v>
+      <c r="D2" s="5">
+        <v>4.25</v>
       </c>
       <c r="E2" s="3"/>
     </row>
@@ -581,8 +517,8 @@
         <v>6</v>
       </c>
       <c r="C3" s="3"/>
-      <c r="D3" s="6" t="s">
-        <v>53</v>
+      <c r="D3" s="5">
+        <v>4.75</v>
       </c>
       <c r="E3" s="1"/>
     </row>
@@ -594,8 +530,8 @@
         <v>7</v>
       </c>
       <c r="C4" s="3"/>
-      <c r="D4" s="5" t="s">
-        <v>54</v>
+      <c r="D4" s="5">
+        <v>7.5</v>
       </c>
       <c r="E4" s="1"/>
     </row>
@@ -607,8 +543,8 @@
         <v>8</v>
       </c>
       <c r="C5" s="1"/>
-      <c r="D5" s="6" t="s">
-        <v>54</v>
+      <c r="D5" s="5">
+        <v>7.5</v>
       </c>
       <c r="E5" s="3"/>
     </row>
@@ -620,8 +556,8 @@
         <v>9</v>
       </c>
       <c r="C6" s="1"/>
-      <c r="D6" s="6" t="s">
-        <v>55</v>
+      <c r="D6" s="5">
+        <v>6.5</v>
       </c>
       <c r="E6" s="1"/>
     </row>
@@ -633,7 +569,7 @@
         <v>10</v>
       </c>
       <c r="C7" s="4"/>
-      <c r="D7" s="7"/>
+      <c r="D7" s="6"/>
       <c r="E7" s="4"/>
     </row>
     <row r="8" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -644,8 +580,8 @@
         <v>11</v>
       </c>
       <c r="C8" s="4"/>
-      <c r="D8" s="7" t="s">
-        <v>56</v>
+      <c r="D8" s="6">
+        <v>0.75</v>
       </c>
       <c r="E8" s="4"/>
     </row>
@@ -657,8 +593,8 @@
         <v>12</v>
       </c>
       <c r="C9" s="4"/>
-      <c r="D9" s="7" t="s">
-        <v>57</v>
+      <c r="D9" s="6">
+        <v>6.25</v>
       </c>
       <c r="E9" s="4"/>
     </row>
@@ -670,8 +606,8 @@
         <v>13</v>
       </c>
       <c r="C10" s="4"/>
-      <c r="D10" s="7" t="s">
-        <v>58</v>
+      <c r="D10" s="6">
+        <v>7</v>
       </c>
       <c r="E10" s="4"/>
     </row>
@@ -683,8 +619,8 @@
         <v>14</v>
       </c>
       <c r="C11" s="4"/>
-      <c r="D11" s="7" t="s">
-        <v>55</v>
+      <c r="D11" s="6">
+        <v>6.5</v>
       </c>
       <c r="E11" s="4"/>
     </row>
@@ -696,8 +632,8 @@
         <v>15</v>
       </c>
       <c r="C12" s="4"/>
-      <c r="D12" s="7" t="s">
-        <v>59</v>
+      <c r="D12" s="6">
+        <v>4.5</v>
       </c>
       <c r="E12" s="4"/>
     </row>
@@ -709,8 +645,8 @@
         <v>16</v>
       </c>
       <c r="C13" s="4"/>
-      <c r="D13" s="7" t="s">
-        <v>60</v>
+      <c r="D13" s="6">
+        <v>6</v>
       </c>
       <c r="E13" s="4"/>
     </row>
@@ -722,8 +658,8 @@
         <v>17</v>
       </c>
       <c r="C14" s="4"/>
-      <c r="D14" s="7" t="s">
-        <v>61</v>
+      <c r="D14" s="6">
+        <v>1.5</v>
       </c>
       <c r="E14" s="4"/>
     </row>
@@ -735,8 +671,8 @@
         <v>18</v>
       </c>
       <c r="C15" s="4"/>
-      <c r="D15" s="7" t="s">
-        <v>62</v>
+      <c r="D15" s="6">
+        <v>6.75</v>
       </c>
       <c r="E15" s="4"/>
     </row>
@@ -748,8 +684,8 @@
         <v>19</v>
       </c>
       <c r="C16" s="4"/>
-      <c r="D16" s="7" t="s">
-        <v>63</v>
+      <c r="D16" s="6">
+        <v>1.75</v>
       </c>
       <c r="E16" s="4"/>
     </row>
@@ -761,8 +697,8 @@
         <v>20</v>
       </c>
       <c r="C17" s="4"/>
-      <c r="D17" s="7" t="s">
-        <v>53</v>
+      <c r="D17" s="6">
+        <v>4.75</v>
       </c>
       <c r="E17" s="4"/>
     </row>
@@ -774,8 +710,8 @@
         <v>21</v>
       </c>
       <c r="C18" s="4"/>
-      <c r="D18" s="7" t="s">
-        <v>64</v>
+      <c r="D18" s="6">
+        <v>5.75</v>
       </c>
       <c r="E18" s="4"/>
     </row>
@@ -787,8 +723,8 @@
         <v>22</v>
       </c>
       <c r="C19" s="4"/>
-      <c r="D19" s="7" t="s">
-        <v>60</v>
+      <c r="D19" s="6">
+        <v>6</v>
       </c>
       <c r="E19" s="4"/>
     </row>
@@ -800,8 +736,8 @@
         <v>23</v>
       </c>
       <c r="C20" s="4"/>
-      <c r="D20" s="7" t="s">
-        <v>62</v>
+      <c r="D20" s="6">
+        <v>6.75</v>
       </c>
       <c r="E20" s="4"/>
     </row>
@@ -813,8 +749,8 @@
         <v>24</v>
       </c>
       <c r="C21" s="4"/>
-      <c r="D21" s="7" t="s">
-        <v>60</v>
+      <c r="D21" s="6">
+        <v>6</v>
       </c>
       <c r="E21" s="4"/>
     </row>
@@ -826,8 +762,8 @@
         <v>25</v>
       </c>
       <c r="C22" s="4"/>
-      <c r="D22" s="7" t="s">
-        <v>65</v>
+      <c r="D22" s="6">
+        <v>8</v>
       </c>
       <c r="E22" s="4"/>
     </row>
@@ -839,8 +775,8 @@
         <v>26</v>
       </c>
       <c r="C23" s="4"/>
-      <c r="D23" s="7" t="s">
-        <v>59</v>
+      <c r="D23" s="6">
+        <v>4.5</v>
       </c>
       <c r="E23" s="4"/>
     </row>
@@ -852,8 +788,8 @@
         <v>27</v>
       </c>
       <c r="C24" s="4"/>
-      <c r="D24" s="7" t="s">
-        <v>66</v>
+      <c r="D24" s="6">
+        <v>7.25</v>
       </c>
       <c r="E24" s="4"/>
     </row>
@@ -865,8 +801,8 @@
         <v>28</v>
       </c>
       <c r="C25" s="4"/>
-      <c r="D25" s="7" t="s">
-        <v>64</v>
+      <c r="D25" s="6">
+        <v>5.75</v>
       </c>
       <c r="E25" s="4"/>
     </row>
@@ -878,8 +814,8 @@
         <v>29</v>
       </c>
       <c r="C26" s="4"/>
-      <c r="D26" s="7" t="s">
-        <v>67</v>
+      <c r="D26" s="6">
+        <v>5.25</v>
       </c>
       <c r="E26" s="4"/>
     </row>
@@ -891,8 +827,8 @@
         <v>30</v>
       </c>
       <c r="C27" s="4"/>
-      <c r="D27" s="7" t="s">
-        <v>68</v>
+      <c r="D27" s="6">
+        <v>5</v>
       </c>
       <c r="E27" s="4"/>
     </row>
@@ -904,8 +840,8 @@
         <v>31</v>
       </c>
       <c r="C28" s="4"/>
-      <c r="D28" s="7" t="s">
-        <v>60</v>
+      <c r="D28" s="6">
+        <v>6</v>
       </c>
       <c r="E28" s="4"/>
     </row>
@@ -917,8 +853,8 @@
         <v>32</v>
       </c>
       <c r="C29" s="4"/>
-      <c r="D29" s="7" t="s">
-        <v>65</v>
+      <c r="D29" s="6">
+        <v>8</v>
       </c>
       <c r="E29" s="4"/>
     </row>
@@ -930,8 +866,8 @@
         <v>33</v>
       </c>
       <c r="C30" s="4"/>
-      <c r="D30" s="7" t="s">
-        <v>68</v>
+      <c r="D30" s="6">
+        <v>5</v>
       </c>
       <c r="E30" s="4"/>
     </row>
@@ -943,8 +879,8 @@
         <v>34</v>
       </c>
       <c r="C31" s="4"/>
-      <c r="D31" s="7" t="s">
-        <v>69</v>
+      <c r="D31" s="6">
+        <v>2.75</v>
       </c>
       <c r="E31" s="4"/>
     </row>
@@ -956,8 +892,8 @@
         <v>35</v>
       </c>
       <c r="C32" s="4"/>
-      <c r="D32" s="7" t="s">
-        <v>57</v>
+      <c r="D32" s="6">
+        <v>6.25</v>
       </c>
       <c r="E32" s="4"/>
     </row>
@@ -969,8 +905,8 @@
         <v>36</v>
       </c>
       <c r="C33" s="4"/>
-      <c r="D33" s="7" t="s">
-        <v>60</v>
+      <c r="D33" s="6">
+        <v>6</v>
       </c>
       <c r="E33" s="4"/>
     </row>
@@ -982,8 +918,8 @@
         <v>37</v>
       </c>
       <c r="C34" s="4"/>
-      <c r="D34" s="7" t="s">
-        <v>64</v>
+      <c r="D34" s="6">
+        <v>5.75</v>
       </c>
       <c r="E34" s="4"/>
     </row>
@@ -995,8 +931,8 @@
         <v>38</v>
       </c>
       <c r="C35" s="4"/>
-      <c r="D35" s="7" t="s">
-        <v>64</v>
+      <c r="D35" s="6">
+        <v>5.75</v>
       </c>
       <c r="E35" s="4"/>
     </row>
@@ -1008,8 +944,8 @@
         <v>39</v>
       </c>
       <c r="C36" s="4"/>
-      <c r="D36" s="7" t="s">
-        <v>57</v>
+      <c r="D36" s="6">
+        <v>6.25</v>
       </c>
       <c r="E36" s="4"/>
     </row>
@@ -1021,8 +957,8 @@
         <v>40</v>
       </c>
       <c r="C37" s="4"/>
-      <c r="D37" s="7" t="s">
-        <v>58</v>
+      <c r="D37" s="6">
+        <v>7</v>
       </c>
       <c r="E37" s="4"/>
     </row>
@@ -1034,8 +970,8 @@
         <v>41</v>
       </c>
       <c r="C38" s="4"/>
-      <c r="D38" s="7" t="s">
-        <v>67</v>
+      <c r="D38" s="6">
+        <v>5.25</v>
       </c>
       <c r="E38" s="4"/>
     </row>
@@ -1047,8 +983,8 @@
         <v>42</v>
       </c>
       <c r="C39" s="4"/>
-      <c r="D39" s="7" t="s">
-        <v>54</v>
+      <c r="D39" s="6">
+        <v>7.5</v>
       </c>
       <c r="E39" s="4"/>
     </row>
@@ -1060,8 +996,8 @@
         <v>43</v>
       </c>
       <c r="C40" s="4"/>
-      <c r="D40" s="7" t="s">
-        <v>59</v>
+      <c r="D40" s="6">
+        <v>4.5</v>
       </c>
       <c r="E40" s="4"/>
     </row>
@@ -1073,8 +1009,8 @@
         <v>44</v>
       </c>
       <c r="C41" s="4"/>
-      <c r="D41" s="7" t="s">
-        <v>70</v>
+      <c r="D41" s="6">
+        <v>5.5</v>
       </c>
       <c r="E41" s="4"/>
     </row>
@@ -1086,8 +1022,8 @@
         <v>45</v>
       </c>
       <c r="C42" s="4"/>
-      <c r="D42" s="7" t="s">
-        <v>71</v>
+      <c r="D42" s="6">
+        <v>4</v>
       </c>
       <c r="E42" s="4"/>
     </row>
@@ -1099,8 +1035,8 @@
         <v>46</v>
       </c>
       <c r="C43" s="4"/>
-      <c r="D43" s="7" t="s">
-        <v>54</v>
+      <c r="D43" s="6">
+        <v>7.5</v>
       </c>
       <c r="E43" s="4"/>
     </row>
@@ -1112,8 +1048,8 @@
         <v>47</v>
       </c>
       <c r="C44" s="4"/>
-      <c r="D44" s="7" t="s">
-        <v>72</v>
+      <c r="D44" s="6">
+        <v>3.75</v>
       </c>
       <c r="E44" s="4"/>
     </row>
@@ -1125,8 +1061,8 @@
         <v>48</v>
       </c>
       <c r="C45" s="4"/>
-      <c r="D45" s="7" t="s">
-        <v>68</v>
+      <c r="D45" s="6">
+        <v>5</v>
       </c>
       <c r="E45" s="4"/>
     </row>
@@ -1138,8 +1074,8 @@
         <v>49</v>
       </c>
       <c r="C46" s="4"/>
-      <c r="D46" s="7" t="s">
-        <v>60</v>
+      <c r="D46" s="6">
+        <v>6</v>
       </c>
       <c r="E46" s="4"/>
     </row>
@@ -1151,8 +1087,8 @@
         <v>50</v>
       </c>
       <c r="C47" s="4"/>
-      <c r="D47" s="7" t="s">
-        <v>60</v>
+      <c r="D47" s="6">
+        <v>6</v>
       </c>
       <c r="E47" s="4"/>
     </row>
@@ -1164,8 +1100,8 @@
         <v>51</v>
       </c>
       <c r="C48" s="4"/>
-      <c r="D48" s="7" t="s">
-        <v>65</v>
+      <c r="D48" s="6">
+        <v>8</v>
       </c>
       <c r="E48" s="4"/>
     </row>

--- a/diem_thi.xlsx
+++ b/diem_thi.xlsx
@@ -239,7 +239,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -250,6 +250,9 @@
     <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -476,6 +479,7 @@
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="24.90625" customWidth="1"/>
+    <col min="3" max="3" width="12.6328125" style="10"/>
     <col min="4" max="4" width="12.6328125" style="7"/>
   </cols>
   <sheetData>
@@ -486,7 +490,7 @@
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="8" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="5" t="s">
@@ -503,7 +507,9 @@
       <c r="B2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="1"/>
+      <c r="C2" s="8">
+        <v>5.25</v>
+      </c>
       <c r="D2" s="5">
         <v>4.25</v>
       </c>
@@ -516,7 +522,9 @@
       <c r="B3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="3"/>
+      <c r="C3" s="8">
+        <v>2.5</v>
+      </c>
       <c r="D3" s="5">
         <v>4.75</v>
       </c>
@@ -529,7 +537,9 @@
       <c r="B4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="3"/>
+      <c r="C4" s="8">
+        <v>7.25</v>
+      </c>
       <c r="D4" s="5">
         <v>7.5</v>
       </c>
@@ -542,7 +552,9 @@
       <c r="B5" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="1"/>
+      <c r="C5" s="8">
+        <v>9</v>
+      </c>
       <c r="D5" s="5">
         <v>7.5</v>
       </c>
@@ -555,7 +567,9 @@
       <c r="B6" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="1"/>
+      <c r="C6" s="8">
+        <v>3.5</v>
+      </c>
       <c r="D6" s="5">
         <v>6.5</v>
       </c>
@@ -568,7 +582,7 @@
       <c r="B7" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="4"/>
+      <c r="C7" s="9"/>
       <c r="D7" s="6"/>
       <c r="E7" s="4"/>
     </row>
@@ -579,7 +593,9 @@
       <c r="B8" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="4"/>
+      <c r="C8" s="9">
+        <v>2.25</v>
+      </c>
       <c r="D8" s="6">
         <v>0.75</v>
       </c>
@@ -592,7 +608,9 @@
       <c r="B9" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="4"/>
+      <c r="C9" s="9">
+        <v>6</v>
+      </c>
       <c r="D9" s="6">
         <v>6.25</v>
       </c>
@@ -605,7 +623,9 @@
       <c r="B10" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="4"/>
+      <c r="C10" s="9">
+        <v>5</v>
+      </c>
       <c r="D10" s="6">
         <v>7</v>
       </c>
@@ -618,7 +638,9 @@
       <c r="B11" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="4"/>
+      <c r="C11" s="9">
+        <v>7.75</v>
+      </c>
       <c r="D11" s="6">
         <v>6.5</v>
       </c>
@@ -631,7 +653,9 @@
       <c r="B12" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="4"/>
+      <c r="C12" s="9">
+        <v>4.5</v>
+      </c>
       <c r="D12" s="6">
         <v>4.5</v>
       </c>
@@ -644,7 +668,9 @@
       <c r="B13" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C13" s="4"/>
+      <c r="C13" s="9">
+        <v>5.25</v>
+      </c>
       <c r="D13" s="6">
         <v>6</v>
       </c>
@@ -657,7 +683,9 @@
       <c r="B14" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C14" s="4"/>
+      <c r="C14" s="9">
+        <v>1</v>
+      </c>
       <c r="D14" s="6">
         <v>1.5</v>
       </c>
@@ -670,7 +698,9 @@
       <c r="B15" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C15" s="4"/>
+      <c r="C15" s="9">
+        <v>8.5</v>
+      </c>
       <c r="D15" s="6">
         <v>6.75</v>
       </c>
@@ -683,7 +713,9 @@
       <c r="B16" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C16" s="4"/>
+      <c r="C16" s="9">
+        <v>3.25</v>
+      </c>
       <c r="D16" s="6">
         <v>1.75</v>
       </c>
@@ -696,7 +728,9 @@
       <c r="B17" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C17" s="4"/>
+      <c r="C17" s="9">
+        <v>4.5</v>
+      </c>
       <c r="D17" s="6">
         <v>4.75</v>
       </c>
@@ -709,7 +743,9 @@
       <c r="B18" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C18" s="4"/>
+      <c r="C18" s="9">
+        <v>5.5</v>
+      </c>
       <c r="D18" s="6">
         <v>5.75</v>
       </c>
@@ -722,7 +758,9 @@
       <c r="B19" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C19" s="4"/>
+      <c r="C19" s="9">
+        <v>6.75</v>
+      </c>
       <c r="D19" s="6">
         <v>6</v>
       </c>
@@ -735,7 +773,9 @@
       <c r="B20" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C20" s="4"/>
+      <c r="C20" s="9">
+        <v>7</v>
+      </c>
       <c r="D20" s="6">
         <v>6.75</v>
       </c>
@@ -748,7 +788,9 @@
       <c r="B21" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C21" s="4"/>
+      <c r="C21" s="9">
+        <v>6.75</v>
+      </c>
       <c r="D21" s="6">
         <v>6</v>
       </c>
@@ -761,7 +803,9 @@
       <c r="B22" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C22" s="4"/>
+      <c r="C22" s="9">
+        <v>7.25</v>
+      </c>
       <c r="D22" s="6">
         <v>8</v>
       </c>
@@ -774,7 +818,9 @@
       <c r="B23" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C23" s="4"/>
+      <c r="C23" s="9">
+        <v>4.25</v>
+      </c>
       <c r="D23" s="6">
         <v>4.5</v>
       </c>
@@ -787,7 +833,9 @@
       <c r="B24" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C24" s="4"/>
+      <c r="C24" s="9">
+        <v>7.25</v>
+      </c>
       <c r="D24" s="6">
         <v>7.25</v>
       </c>
@@ -800,7 +848,9 @@
       <c r="B25" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C25" s="4"/>
+      <c r="C25" s="9">
+        <v>5.75</v>
+      </c>
       <c r="D25" s="6">
         <v>5.75</v>
       </c>
@@ -813,7 +863,9 @@
       <c r="B26" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C26" s="4"/>
+      <c r="C26" s="9">
+        <v>8.25</v>
+      </c>
       <c r="D26" s="6">
         <v>5.25</v>
       </c>
@@ -826,7 +878,9 @@
       <c r="B27" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C27" s="4"/>
+      <c r="C27" s="9">
+        <v>5.5</v>
+      </c>
       <c r="D27" s="6">
         <v>5</v>
       </c>
@@ -839,7 +893,9 @@
       <c r="B28" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C28" s="4"/>
+      <c r="C28" s="9">
+        <v>7</v>
+      </c>
       <c r="D28" s="6">
         <v>6</v>
       </c>
@@ -852,7 +908,9 @@
       <c r="B29" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C29" s="4"/>
+      <c r="C29" s="9">
+        <v>5.5</v>
+      </c>
       <c r="D29" s="6">
         <v>8</v>
       </c>
@@ -865,7 +923,9 @@
       <c r="B30" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C30" s="4"/>
+      <c r="C30" s="9">
+        <v>6.5</v>
+      </c>
       <c r="D30" s="6">
         <v>5</v>
       </c>
@@ -878,7 +938,9 @@
       <c r="B31" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C31" s="4"/>
+      <c r="C31" s="9">
+        <v>3.75</v>
+      </c>
       <c r="D31" s="6">
         <v>2.75</v>
       </c>
@@ -891,7 +953,9 @@
       <c r="B32" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C32" s="4"/>
+      <c r="C32" s="9">
+        <v>5.75</v>
+      </c>
       <c r="D32" s="6">
         <v>6.25</v>
       </c>
@@ -904,7 +968,9 @@
       <c r="B33" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C33" s="4"/>
+      <c r="C33" s="9">
+        <v>6.5</v>
+      </c>
       <c r="D33" s="6">
         <v>6</v>
       </c>
@@ -917,7 +983,9 @@
       <c r="B34" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C34" s="4"/>
+      <c r="C34" s="9">
+        <v>4</v>
+      </c>
       <c r="D34" s="6">
         <v>5.75</v>
       </c>
@@ -930,7 +998,9 @@
       <c r="B35" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C35" s="4"/>
+      <c r="C35" s="9">
+        <v>5.75</v>
+      </c>
       <c r="D35" s="6">
         <v>5.75</v>
       </c>
@@ -943,7 +1013,9 @@
       <c r="B36" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C36" s="4"/>
+      <c r="C36" s="9">
+        <v>8</v>
+      </c>
       <c r="D36" s="6">
         <v>6.25</v>
       </c>
@@ -956,7 +1028,9 @@
       <c r="B37" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C37" s="4"/>
+      <c r="C37" s="9">
+        <v>5.75</v>
+      </c>
       <c r="D37" s="6">
         <v>7</v>
       </c>
@@ -969,7 +1043,9 @@
       <c r="B38" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C38" s="4"/>
+      <c r="C38" s="9">
+        <v>7.25</v>
+      </c>
       <c r="D38" s="6">
         <v>5.25</v>
       </c>
@@ -982,7 +1058,9 @@
       <c r="B39" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C39" s="4"/>
+      <c r="C39" s="9">
+        <v>8.25</v>
+      </c>
       <c r="D39" s="6">
         <v>7.5</v>
       </c>
@@ -995,7 +1073,9 @@
       <c r="B40" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C40" s="4"/>
+      <c r="C40" s="9">
+        <v>2.5</v>
+      </c>
       <c r="D40" s="6">
         <v>4.5</v>
       </c>
@@ -1008,7 +1088,9 @@
       <c r="B41" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C41" s="4"/>
+      <c r="C41" s="9">
+        <v>4.5</v>
+      </c>
       <c r="D41" s="6">
         <v>5.5</v>
       </c>
@@ -1021,7 +1103,9 @@
       <c r="B42" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C42" s="4"/>
+      <c r="C42" s="9">
+        <v>4.75</v>
+      </c>
       <c r="D42" s="6">
         <v>4</v>
       </c>
@@ -1034,7 +1118,9 @@
       <c r="B43" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C43" s="4"/>
+      <c r="C43" s="9">
+        <v>7.75</v>
+      </c>
       <c r="D43" s="6">
         <v>7.5</v>
       </c>
@@ -1047,7 +1133,9 @@
       <c r="B44" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C44" s="4"/>
+      <c r="C44" s="9">
+        <v>1.75</v>
+      </c>
       <c r="D44" s="6">
         <v>3.75</v>
       </c>
@@ -1060,7 +1148,9 @@
       <c r="B45" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="C45" s="4"/>
+      <c r="C45" s="9">
+        <v>4.5</v>
+      </c>
       <c r="D45" s="6">
         <v>5</v>
       </c>
@@ -1073,7 +1163,9 @@
       <c r="B46" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C46" s="4"/>
+      <c r="C46" s="9">
+        <v>7</v>
+      </c>
       <c r="D46" s="6">
         <v>6</v>
       </c>
@@ -1086,7 +1178,9 @@
       <c r="B47" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C47" s="4"/>
+      <c r="C47" s="9">
+        <v>4.75</v>
+      </c>
       <c r="D47" s="6">
         <v>6</v>
       </c>
@@ -1099,7 +1193,9 @@
       <c r="B48" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C48" s="4"/>
+      <c r="C48" s="9">
+        <v>7.75</v>
+      </c>
       <c r="D48" s="6">
         <v>8</v>
       </c>

--- a/diem_thi.xlsx
+++ b/diem_thi.xlsx
@@ -181,9 +181,6 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="d\.m"/>
-  </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -239,14 +236,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -479,8 +474,8 @@
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="24.90625" customWidth="1"/>
-    <col min="3" max="3" width="12.6328125" style="10"/>
-    <col min="4" max="4" width="12.6328125" style="7"/>
+    <col min="3" max="3" width="12.6328125" style="8"/>
+    <col min="4" max="4" width="12.6328125" style="5"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -490,10 +485,10 @@
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
@@ -507,13 +502,15 @@
       <c r="B2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="8">
+      <c r="C2" s="6">
         <v>5.25</v>
       </c>
-      <c r="D2" s="5">
+      <c r="D2" s="3">
         <v>4.25</v>
       </c>
-      <c r="E2" s="3"/>
+      <c r="E2" s="6">
+        <v>2.4</v>
+      </c>
     </row>
     <row r="3" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
@@ -522,13 +519,15 @@
       <c r="B3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="8">
+      <c r="C3" s="6">
         <v>2.5</v>
       </c>
-      <c r="D3" s="5">
+      <c r="D3" s="3">
         <v>4.75</v>
       </c>
-      <c r="E3" s="1"/>
+      <c r="E3" s="6">
+        <v>2.2000000000000002</v>
+      </c>
     </row>
     <row r="4" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
@@ -537,13 +536,15 @@
       <c r="B4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="8">
+      <c r="C4" s="6">
         <v>7.25</v>
       </c>
-      <c r="D4" s="5">
+      <c r="D4" s="3">
         <v>7.5</v>
       </c>
-      <c r="E4" s="1"/>
+      <c r="E4" s="6">
+        <v>6.4</v>
+      </c>
     </row>
     <row r="5" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
@@ -552,13 +553,15 @@
       <c r="B5" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="8">
+      <c r="C5" s="6">
         <v>9</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D5" s="3">
         <v>7.5</v>
       </c>
-      <c r="E5" s="3"/>
+      <c r="E5" s="6">
+        <v>6.8</v>
+      </c>
     </row>
     <row r="6" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
@@ -567,13 +570,15 @@
       <c r="B6" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="8">
+      <c r="C6" s="6">
         <v>3.5</v>
       </c>
-      <c r="D6" s="5">
+      <c r="D6" s="3">
         <v>6.5</v>
       </c>
-      <c r="E6" s="1"/>
+      <c r="E6" s="6">
+        <v>2.8</v>
+      </c>
     </row>
     <row r="7" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
@@ -582,9 +587,9 @@
       <c r="B7" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="9"/>
-      <c r="D7" s="6"/>
-      <c r="E7" s="4"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="7"/>
     </row>
     <row r="8" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
@@ -593,13 +598,15 @@
       <c r="B8" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="9">
+      <c r="C8" s="7">
         <v>2.25</v>
       </c>
-      <c r="D8" s="6">
+      <c r="D8" s="4">
         <v>0.75</v>
       </c>
-      <c r="E8" s="4"/>
+      <c r="E8" s="7">
+        <v>1.4</v>
+      </c>
     </row>
     <row r="9" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
@@ -608,13 +615,15 @@
       <c r="B9" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="9">
+      <c r="C9" s="7">
         <v>6</v>
       </c>
-      <c r="D9" s="6">
+      <c r="D9" s="4">
         <v>6.25</v>
       </c>
-      <c r="E9" s="4"/>
+      <c r="E9" s="7">
+        <v>3</v>
+      </c>
     </row>
     <row r="10" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
@@ -623,13 +632,15 @@
       <c r="B10" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="9">
+      <c r="C10" s="7">
         <v>5</v>
       </c>
-      <c r="D10" s="6">
+      <c r="D10" s="4">
         <v>7</v>
       </c>
-      <c r="E10" s="4"/>
+      <c r="E10" s="7">
+        <v>2.6</v>
+      </c>
     </row>
     <row r="11" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
@@ -638,13 +649,15 @@
       <c r="B11" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="9">
+      <c r="C11" s="7">
         <v>7.75</v>
       </c>
-      <c r="D11" s="6">
+      <c r="D11" s="4">
         <v>6.5</v>
       </c>
-      <c r="E11" s="4"/>
+      <c r="E11" s="7">
+        <v>3.2</v>
+      </c>
     </row>
     <row r="12" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
@@ -653,13 +666,15 @@
       <c r="B12" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="9">
+      <c r="C12" s="7">
         <v>4.5</v>
       </c>
-      <c r="D12" s="6">
+      <c r="D12" s="4">
         <v>4.5</v>
       </c>
-      <c r="E12" s="4"/>
+      <c r="E12" s="7">
+        <v>1.6</v>
+      </c>
     </row>
     <row r="13" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
@@ -668,13 +683,15 @@
       <c r="B13" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C13" s="9">
+      <c r="C13" s="7">
         <v>5.25</v>
       </c>
-      <c r="D13" s="6">
+      <c r="D13" s="4">
         <v>6</v>
       </c>
-      <c r="E13" s="4"/>
+      <c r="E13" s="7">
+        <v>3.6</v>
+      </c>
     </row>
     <row r="14" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
@@ -683,13 +700,15 @@
       <c r="B14" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C14" s="9">
+      <c r="C14" s="7">
         <v>1</v>
       </c>
-      <c r="D14" s="6">
+      <c r="D14" s="4">
         <v>1.5</v>
       </c>
-      <c r="E14" s="4"/>
+      <c r="E14" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="15" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
@@ -698,13 +717,15 @@
       <c r="B15" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C15" s="9">
+      <c r="C15" s="7">
         <v>8.5</v>
       </c>
-      <c r="D15" s="6">
+      <c r="D15" s="4">
         <v>6.75</v>
       </c>
-      <c r="E15" s="4"/>
+      <c r="E15" s="7">
+        <v>5.6</v>
+      </c>
     </row>
     <row r="16" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
@@ -713,13 +734,15 @@
       <c r="B16" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C16" s="9">
+      <c r="C16" s="7">
         <v>3.25</v>
       </c>
-      <c r="D16" s="6">
+      <c r="D16" s="4">
         <v>1.75</v>
       </c>
-      <c r="E16" s="4"/>
+      <c r="E16" s="7">
+        <v>2.8</v>
+      </c>
     </row>
     <row r="17" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
@@ -728,13 +751,15 @@
       <c r="B17" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C17" s="9">
+      <c r="C17" s="7">
         <v>4.5</v>
       </c>
-      <c r="D17" s="6">
+      <c r="D17" s="4">
         <v>4.75</v>
       </c>
-      <c r="E17" s="4"/>
+      <c r="E17" s="7">
+        <v>3.4</v>
+      </c>
     </row>
     <row r="18" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
@@ -743,13 +768,15 @@
       <c r="B18" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C18" s="9">
+      <c r="C18" s="7">
         <v>5.5</v>
       </c>
-      <c r="D18" s="6">
+      <c r="D18" s="4">
         <v>5.75</v>
       </c>
-      <c r="E18" s="4"/>
+      <c r="E18" s="7">
+        <v>1.6</v>
+      </c>
     </row>
     <row r="19" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
@@ -758,13 +785,15 @@
       <c r="B19" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C19" s="9">
+      <c r="C19" s="7">
         <v>6.75</v>
       </c>
-      <c r="D19" s="6">
+      <c r="D19" s="4">
         <v>6</v>
       </c>
-      <c r="E19" s="4"/>
+      <c r="E19" s="7">
+        <v>5</v>
+      </c>
     </row>
     <row r="20" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
@@ -773,13 +802,15 @@
       <c r="B20" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C20" s="9">
+      <c r="C20" s="7">
         <v>7</v>
       </c>
-      <c r="D20" s="6">
+      <c r="D20" s="4">
         <v>6.75</v>
       </c>
-      <c r="E20" s="4"/>
+      <c r="E20" s="7">
+        <v>6.4</v>
+      </c>
     </row>
     <row r="21" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
@@ -788,13 +819,15 @@
       <c r="B21" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C21" s="9">
+      <c r="C21" s="7">
         <v>6.75</v>
       </c>
-      <c r="D21" s="6">
+      <c r="D21" s="4">
         <v>6</v>
       </c>
-      <c r="E21" s="4"/>
+      <c r="E21" s="7">
+        <v>2.6</v>
+      </c>
     </row>
     <row r="22" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
@@ -803,13 +836,15 @@
       <c r="B22" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C22" s="9">
+      <c r="C22" s="7">
         <v>7.25</v>
       </c>
-      <c r="D22" s="6">
+      <c r="D22" s="4">
         <v>8</v>
       </c>
-      <c r="E22" s="4"/>
+      <c r="E22" s="7">
+        <v>4.4000000000000004</v>
+      </c>
     </row>
     <row r="23" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
@@ -818,13 +853,15 @@
       <c r="B23" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C23" s="9">
+      <c r="C23" s="7">
         <v>4.25</v>
       </c>
-      <c r="D23" s="6">
+      <c r="D23" s="4">
         <v>4.5</v>
       </c>
-      <c r="E23" s="4"/>
+      <c r="E23" s="7">
+        <v>2.2000000000000002</v>
+      </c>
     </row>
     <row r="24" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
@@ -833,13 +870,15 @@
       <c r="B24" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C24" s="9">
+      <c r="C24" s="7">
         <v>7.25</v>
       </c>
-      <c r="D24" s="6">
+      <c r="D24" s="4">
         <v>7.25</v>
       </c>
-      <c r="E24" s="4"/>
+      <c r="E24" s="7">
+        <v>5</v>
+      </c>
     </row>
     <row r="25" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
@@ -848,13 +887,15 @@
       <c r="B25" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C25" s="9">
+      <c r="C25" s="7">
         <v>5.75</v>
       </c>
-      <c r="D25" s="6">
+      <c r="D25" s="4">
         <v>5.75</v>
       </c>
-      <c r="E25" s="4"/>
+      <c r="E25" s="7">
+        <v>2.6</v>
+      </c>
     </row>
     <row r="26" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
@@ -863,13 +904,15 @@
       <c r="B26" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C26" s="9">
+      <c r="C26" s="7">
         <v>8.25</v>
       </c>
-      <c r="D26" s="6">
+      <c r="D26" s="4">
         <v>5.25</v>
       </c>
-      <c r="E26" s="4"/>
+      <c r="E26" s="7">
+        <v>5.4</v>
+      </c>
     </row>
     <row r="27" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
@@ -878,13 +921,15 @@
       <c r="B27" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C27" s="9">
+      <c r="C27" s="7">
         <v>5.5</v>
       </c>
-      <c r="D27" s="6">
+      <c r="D27" s="4">
         <v>5</v>
       </c>
-      <c r="E27" s="4"/>
+      <c r="E27" s="7">
+        <v>4</v>
+      </c>
     </row>
     <row r="28" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
@@ -893,13 +938,15 @@
       <c r="B28" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C28" s="9">
+      <c r="C28" s="7">
         <v>7</v>
       </c>
-      <c r="D28" s="6">
+      <c r="D28" s="4">
         <v>6</v>
       </c>
-      <c r="E28" s="4"/>
+      <c r="E28" s="7">
+        <v>5</v>
+      </c>
     </row>
     <row r="29" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
@@ -908,13 +955,15 @@
       <c r="B29" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C29" s="9">
+      <c r="C29" s="7">
         <v>5.5</v>
       </c>
-      <c r="D29" s="6">
+      <c r="D29" s="4">
         <v>8</v>
       </c>
-      <c r="E29" s="4"/>
+      <c r="E29" s="7">
+        <v>3.6</v>
+      </c>
     </row>
     <row r="30" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
@@ -923,13 +972,15 @@
       <c r="B30" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C30" s="9">
+      <c r="C30" s="7">
         <v>6.5</v>
       </c>
-      <c r="D30" s="6">
+      <c r="D30" s="4">
         <v>5</v>
       </c>
-      <c r="E30" s="4"/>
+      <c r="E30" s="7">
+        <v>2.8</v>
+      </c>
     </row>
     <row r="31" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
@@ -938,13 +989,15 @@
       <c r="B31" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C31" s="9">
+      <c r="C31" s="7">
         <v>3.75</v>
       </c>
-      <c r="D31" s="6">
+      <c r="D31" s="4">
         <v>2.75</v>
       </c>
-      <c r="E31" s="4"/>
+      <c r="E31" s="7">
+        <v>1.4</v>
+      </c>
     </row>
     <row r="32" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
@@ -953,13 +1006,15 @@
       <c r="B32" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C32" s="9">
+      <c r="C32" s="7">
         <v>5.75</v>
       </c>
-      <c r="D32" s="6">
+      <c r="D32" s="4">
         <v>6.25</v>
       </c>
-      <c r="E32" s="4"/>
+      <c r="E32" s="7">
+        <v>1.2</v>
+      </c>
     </row>
     <row r="33" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
@@ -968,13 +1023,15 @@
       <c r="B33" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C33" s="9">
+      <c r="C33" s="7">
         <v>6.5</v>
       </c>
-      <c r="D33" s="6">
+      <c r="D33" s="4">
         <v>6</v>
       </c>
-      <c r="E33" s="4"/>
+      <c r="E33" s="7">
+        <v>3.8</v>
+      </c>
     </row>
     <row r="34" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
@@ -983,13 +1040,15 @@
       <c r="B34" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C34" s="9">
+      <c r="C34" s="7">
         <v>4</v>
       </c>
-      <c r="D34" s="6">
+      <c r="D34" s="4">
         <v>5.75</v>
       </c>
-      <c r="E34" s="4"/>
+      <c r="E34" s="7">
+        <v>2.6</v>
+      </c>
     </row>
     <row r="35" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
@@ -998,13 +1057,15 @@
       <c r="B35" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C35" s="9">
+      <c r="C35" s="7">
         <v>5.75</v>
       </c>
-      <c r="D35" s="6">
+      <c r="D35" s="4">
         <v>5.75</v>
       </c>
-      <c r="E35" s="4"/>
+      <c r="E35" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="36" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
@@ -1013,13 +1074,15 @@
       <c r="B36" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C36" s="9">
+      <c r="C36" s="7">
         <v>8</v>
       </c>
-      <c r="D36" s="6">
+      <c r="D36" s="4">
         <v>6.25</v>
       </c>
-      <c r="E36" s="4"/>
+      <c r="E36" s="7">
+        <v>8.1999999999999993</v>
+      </c>
     </row>
     <row r="37" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
@@ -1028,13 +1091,15 @@
       <c r="B37" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C37" s="9">
+      <c r="C37" s="7">
         <v>5.75</v>
       </c>
-      <c r="D37" s="6">
+      <c r="D37" s="4">
         <v>7</v>
       </c>
-      <c r="E37" s="4"/>
+      <c r="E37" s="7">
+        <v>4</v>
+      </c>
     </row>
     <row r="38" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
@@ -1043,13 +1108,15 @@
       <c r="B38" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C38" s="9">
+      <c r="C38" s="7">
         <v>7.25</v>
       </c>
-      <c r="D38" s="6">
+      <c r="D38" s="4">
         <v>5.25</v>
       </c>
-      <c r="E38" s="4"/>
+      <c r="E38" s="7">
+        <v>3.2</v>
+      </c>
     </row>
     <row r="39" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
@@ -1058,13 +1125,15 @@
       <c r="B39" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C39" s="9">
+      <c r="C39" s="7">
         <v>8.25</v>
       </c>
-      <c r="D39" s="6">
+      <c r="D39" s="4">
         <v>7.5</v>
       </c>
-      <c r="E39" s="4"/>
+      <c r="E39" s="7">
+        <v>5.2</v>
+      </c>
     </row>
     <row r="40" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
@@ -1073,13 +1142,15 @@
       <c r="B40" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C40" s="9">
+      <c r="C40" s="7">
         <v>2.5</v>
       </c>
-      <c r="D40" s="6">
+      <c r="D40" s="4">
         <v>4.5</v>
       </c>
-      <c r="E40" s="4"/>
+      <c r="E40" s="7">
+        <v>3</v>
+      </c>
     </row>
     <row r="41" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
@@ -1088,13 +1159,15 @@
       <c r="B41" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C41" s="9">
+      <c r="C41" s="7">
         <v>4.5</v>
       </c>
-      <c r="D41" s="6">
+      <c r="D41" s="4">
         <v>5.5</v>
       </c>
-      <c r="E41" s="4"/>
+      <c r="E41" s="7">
+        <v>2.8</v>
+      </c>
     </row>
     <row r="42" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
@@ -1103,13 +1176,15 @@
       <c r="B42" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C42" s="9">
+      <c r="C42" s="7">
         <v>4.75</v>
       </c>
-      <c r="D42" s="6">
+      <c r="D42" s="4">
         <v>4</v>
       </c>
-      <c r="E42" s="4"/>
+      <c r="E42" s="7">
+        <v>3.4</v>
+      </c>
     </row>
     <row r="43" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
@@ -1118,13 +1193,15 @@
       <c r="B43" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C43" s="9">
+      <c r="C43" s="7">
         <v>7.75</v>
       </c>
-      <c r="D43" s="6">
+      <c r="D43" s="4">
         <v>7.5</v>
       </c>
-      <c r="E43" s="4"/>
+      <c r="E43" s="7">
+        <v>9.4</v>
+      </c>
     </row>
     <row r="44" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
@@ -1133,13 +1210,15 @@
       <c r="B44" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C44" s="9">
+      <c r="C44" s="7">
         <v>1.75</v>
       </c>
-      <c r="D44" s="6">
+      <c r="D44" s="4">
         <v>3.75</v>
       </c>
-      <c r="E44" s="4"/>
+      <c r="E44" s="7">
+        <v>1.6</v>
+      </c>
     </row>
     <row r="45" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
@@ -1148,13 +1227,15 @@
       <c r="B45" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="C45" s="9">
+      <c r="C45" s="7">
         <v>4.5</v>
       </c>
-      <c r="D45" s="6">
+      <c r="D45" s="4">
         <v>5</v>
       </c>
-      <c r="E45" s="4"/>
+      <c r="E45" s="7">
+        <v>3.8</v>
+      </c>
     </row>
     <row r="46" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
@@ -1163,13 +1244,15 @@
       <c r="B46" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C46" s="9">
+      <c r="C46" s="7">
         <v>7</v>
       </c>
-      <c r="D46" s="6">
+      <c r="D46" s="4">
         <v>6</v>
       </c>
-      <c r="E46" s="4"/>
+      <c r="E46" s="7">
+        <v>5.4</v>
+      </c>
     </row>
     <row r="47" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
@@ -1178,13 +1261,15 @@
       <c r="B47" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C47" s="9">
+      <c r="C47" s="7">
         <v>4.75</v>
       </c>
-      <c r="D47" s="6">
+      <c r="D47" s="4">
         <v>6</v>
       </c>
-      <c r="E47" s="4"/>
+      <c r="E47" s="7">
+        <v>2</v>
+      </c>
     </row>
     <row r="48" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
@@ -1193,13 +1278,15 @@
       <c r="B48" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C48" s="9">
+      <c r="C48" s="7">
         <v>7.75</v>
       </c>
-      <c r="D48" s="6">
+      <c r="D48" s="4">
         <v>8</v>
       </c>
-      <c r="E48" s="4"/>
+      <c r="E48" s="7">
+        <v>8.4</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
